--- a/demo-data/olivine_demo_depot_sto.xlsx
+++ b/demo-data/olivine_demo_depot_sto.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10674</v>
+        <v>7388</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>662.99</v>
+        <v>462.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17.10.26</t>
+          <t>05.08.26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7033</v>
+        <v>3227</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>685.76</v>
+        <v>124.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6910</v>
+        <v>4816</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>235.11</v>
+        <v>482.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13111</v>
+        <v>10547</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>381.48</v>
+        <v>521.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11.10.26</t>
+          <t>27.09.26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13447</v>
+        <v>5538</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>485.47</v>
+        <v>499.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15.10.26</t>
+          <t>26.08.26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10527</v>
+        <v>14167</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>360.91</v>
+        <v>532.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8948</v>
+        <v>11262</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -783,13 +783,13 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>646.65</v>
+        <v>130.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.10.26</t>
+          <t>14.09.26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12515</v>
+        <v>8751</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>336.12</v>
+        <v>622.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18.10.26</t>
+          <t>24.09.26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4546</v>
+        <v>11280</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -869,13 +869,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>201.87</v>
+        <v>634.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21.10.26</t>
+          <t>16.08.26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6188</v>
+        <v>8423</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>212.64</v>
+        <v>674.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13.10.26</t>
+          <t>22.09.26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3295</v>
+        <v>5660</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>478.72</v>
+        <v>362.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07.10.26</t>
+          <t>08.08.26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4829</v>
+        <v>12056</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>453.57</v>
+        <v>318.61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12.10.26</t>
+          <t>26.09.26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7376</v>
+        <v>6960</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1041,7 +1041,93 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>667.28</v>
+        <v>181.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>28.09.26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Olivine</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bhola Enterprises</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AMARAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>INV-7300</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ACD2345</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kwekwe</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>27.09.26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hypery</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PNP Stores</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>WILLAND</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>INV-7301</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AHE0473</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Chitungwiza</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>298.5</v>
       </c>
     </row>
   </sheetData>
